--- a/frontend/public/weekly_contest_4_leaderboard.xlsx
+++ b/frontend/public/weekly_contest_4_leaderboard.xlsx
@@ -11,11 +11,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>Name</t>
   </si>
   <si>
+    <t>Email</t>
+  </si>
+  <si>
     <t>Total Score 500.0</t>
   </si>
   <si>
@@ -28,64 +31,127 @@
     <t>HARSHITH S DEVADIGA</t>
   </si>
   <si>
+    <t>nnm23cc018@nmamit.in</t>
+  </si>
+  <si>
     <t>Anvith C Bhagavath</t>
   </si>
   <si>
+    <t>nnm23cc007@nmamit.in</t>
+  </si>
+  <si>
     <t>NNM24CS253 SRISTI K</t>
   </si>
   <si>
+    <t>nnm24cs253@nmamit.in</t>
+  </si>
+  <si>
     <t>Pranavraj P Achar</t>
   </si>
   <si>
+    <t>nnm23is133@nmamit.in</t>
+  </si>
+  <si>
     <t>Vinyasa Vijendra Prabhu</t>
   </si>
   <si>
+    <t>nnm24is280@nmamit.in</t>
+  </si>
+  <si>
     <t>Shravya .</t>
   </si>
   <si>
+    <t>nnm24cs235@nmamit.in</t>
+  </si>
+  <si>
     <t>Aman Hegde</t>
   </si>
   <si>
+    <t>nnm24is019@nmamit.in</t>
+  </si>
+  <si>
     <t>Parimi Saketh Kumar</t>
   </si>
   <si>
+    <t>nnm23cs123@nmamit.in</t>
+  </si>
+  <si>
     <t>HARSHITHA SHETTIGAR</t>
   </si>
   <si>
+    <t>nnm24vl016@nmamit.in</t>
+  </si>
+  <si>
     <t>anvith poojary</t>
   </si>
   <si>
+    <t>anvithpoojary07@gmail.com</t>
+  </si>
+  <si>
     <t>Sachith G Anchan</t>
   </si>
   <si>
+    <t>sachithanchan@gmail.com</t>
+  </si>
+  <si>
     <t>Atmika Nayak</t>
   </si>
   <si>
+    <t>atmikanayak021206@gmail.com</t>
+  </si>
+  <si>
     <t>Prajwal Inna</t>
   </si>
   <si>
+    <t>nnm23cs132@nmamit.in</t>
+  </si>
+  <si>
     <t>SHREYA G AMIN</t>
   </si>
   <si>
+    <t>nnm24cs352@nmamit.in</t>
+  </si>
+  <si>
     <t>Shamya S Shetty</t>
   </si>
   <si>
+    <t>nnm24cs226@nmamit.in</t>
+  </si>
+  <si>
     <t>Amish Sudhakara</t>
   </si>
   <si>
+    <t>amishs2006@gmail.com</t>
+  </si>
+  <si>
     <t>Ashwitha</t>
   </si>
   <si>
+    <t>nnm23cc010@nmamit.in</t>
+  </si>
+  <si>
     <t>Nihal Shetty</t>
   </si>
   <si>
+    <t>nihalhshetty30@gmail.com</t>
+  </si>
+  <si>
     <t>aadish salian</t>
   </si>
   <si>
+    <t>salianaadish@gmail.com</t>
+  </si>
+  <si>
     <t>REESHAL SUVARNA</t>
   </si>
   <si>
+    <t>nnm23is146@nmamit.in</t>
+  </si>
+  <si>
     <t>B. Shreya Kamath</t>
+  </si>
+  <si>
+    <t>bshreyakamath@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -358,9 +424,9 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="22.63"/>
-    <col customWidth="1" min="2" max="2" width="14.38"/>
-    <col customWidth="1" min="3" max="3" width="14.88"/>
-    <col customWidth="1" min="4" max="4" width="15.63"/>
+    <col customWidth="1" min="2" max="3" width="14.38"/>
+    <col customWidth="1" min="4" max="4" width="14.88"/>
+    <col customWidth="1" min="5" max="5" width="15.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -376,298 +442,364 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="3">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3">
         <v>380.0</v>
       </c>
-      <c r="C2" s="3">
-        <v>500.0</v>
-      </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
+        <v>500.0</v>
+      </c>
+      <c r="E2" s="4">
         <v>0.04815972222222222</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="3">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3">
         <v>370.0</v>
       </c>
-      <c r="C3" s="3">
-        <v>500.0</v>
-      </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
+        <v>500.0</v>
+      </c>
+      <c r="E3" s="4">
         <v>0.049074074074074076</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="3">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3">
         <v>360.0</v>
       </c>
-      <c r="C4" s="3">
-        <v>500.0</v>
-      </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
+        <v>500.0</v>
+      </c>
+      <c r="E4" s="4">
         <v>0.054224537037037036</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="3">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3">
         <v>300.0</v>
       </c>
-      <c r="C5" s="3">
-        <v>500.0</v>
-      </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
+        <v>500.0</v>
+      </c>
+      <c r="E5" s="4">
         <v>0.025219907407407406</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="3">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="3">
         <v>250.0</v>
       </c>
-      <c r="C6" s="3">
-        <v>500.0</v>
-      </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
+        <v>500.0</v>
+      </c>
+      <c r="E6" s="4">
         <v>0.04331018518518519</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="3">
+        <v>15</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="3">
         <v>240.0</v>
       </c>
-      <c r="C7" s="3">
-        <v>500.0</v>
-      </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
+        <v>500.0</v>
+      </c>
+      <c r="E7" s="4">
         <v>0.02991898148148148</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="3">
+        <v>17</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3">
         <v>230.0</v>
       </c>
-      <c r="C8" s="3">
-        <v>500.0</v>
-      </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
+        <v>500.0</v>
+      </c>
+      <c r="E8" s="4">
         <v>0.04814814814814815</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="3">
+        <v>19</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="3">
         <v>210.0</v>
       </c>
-      <c r="C9" s="3">
-        <v>500.0</v>
-      </c>
-      <c r="D9" s="4">
+      <c r="D9" s="3">
+        <v>500.0</v>
+      </c>
+      <c r="E9" s="4">
         <v>0.029386574074074075</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="3">
+        <v>21</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="3">
         <v>200.0</v>
       </c>
-      <c r="C10" s="3">
-        <v>500.0</v>
-      </c>
-      <c r="D10" s="4">
+      <c r="D10" s="3">
+        <v>500.0</v>
+      </c>
+      <c r="E10" s="4">
         <v>0.033344907407407406</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="3">
+        <v>23</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="3">
         <v>200.0</v>
       </c>
-      <c r="C11" s="3">
-        <v>500.0</v>
-      </c>
-      <c r="D11" s="4">
+      <c r="D11" s="3">
+        <v>500.0</v>
+      </c>
+      <c r="E11" s="4">
         <v>0.03422453703703704</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="3">
+        <v>25</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="3">
         <v>170.0</v>
       </c>
-      <c r="C12" s="3">
-        <v>500.0</v>
-      </c>
-      <c r="D12" s="4">
+      <c r="D12" s="3">
+        <v>500.0</v>
+      </c>
+      <c r="E12" s="4">
         <v>0.05407407407407407</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="3">
+        <v>27</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="3">
         <v>150.0</v>
       </c>
-      <c r="C13" s="3">
-        <v>500.0</v>
-      </c>
-      <c r="D13" s="4">
+      <c r="D13" s="3">
+        <v>500.0</v>
+      </c>
+      <c r="E13" s="4">
         <v>0.04777777777777778</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="3">
+        <v>29</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="3">
         <v>80.0</v>
       </c>
-      <c r="C14" s="3">
-        <v>500.0</v>
-      </c>
-      <c r="D14" s="4">
+      <c r="D14" s="3">
+        <v>500.0</v>
+      </c>
+      <c r="E14" s="4">
         <v>0.05206018518518519</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="3">
+        <v>31</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="3">
         <v>50.0</v>
       </c>
-      <c r="C15" s="3">
-        <v>500.0</v>
-      </c>
-      <c r="D15" s="4">
+      <c r="D15" s="3">
+        <v>500.0</v>
+      </c>
+      <c r="E15" s="4">
         <v>0.017974537037037035</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="3">
+        <v>33</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="3">
         <v>50.0</v>
       </c>
-      <c r="C16" s="3">
-        <v>500.0</v>
-      </c>
-      <c r="D16" s="4">
+      <c r="D16" s="3">
+        <v>500.0</v>
+      </c>
+      <c r="E16" s="4">
         <v>0.057743055555555554</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="3">
+        <v>35</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="3">
         <v>40.0</v>
       </c>
-      <c r="C17" s="3">
-        <v>500.0</v>
-      </c>
-      <c r="D17" s="4">
+      <c r="D17" s="3">
+        <v>500.0</v>
+      </c>
+      <c r="E17" s="4">
         <v>0.05271990740740741</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="3">
+        <v>37</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="3">
         <v>20.0</v>
       </c>
-      <c r="C18" s="3">
-        <v>500.0</v>
-      </c>
-      <c r="D18" s="4">
+      <c r="D18" s="3">
+        <v>500.0</v>
+      </c>
+      <c r="E18" s="4">
         <v>0.023032407407407408</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="3">
+        <v>39</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="3">
         <v>20.0</v>
       </c>
-      <c r="C19" s="3">
-        <v>500.0</v>
-      </c>
-      <c r="D19" s="4">
+      <c r="D19" s="3">
+        <v>500.0</v>
+      </c>
+      <c r="E19" s="4">
         <v>0.023842592592592592</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="3">
+        <v>41</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="3">
         <v>20.0</v>
       </c>
-      <c r="C20" s="3">
-        <v>500.0</v>
-      </c>
-      <c r="D20" s="4">
+      <c r="D20" s="3">
+        <v>500.0</v>
+      </c>
+      <c r="E20" s="4">
         <v>0.028368055555555556</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="3">
+        <v>43</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="3">
         <v>20.0</v>
       </c>
-      <c r="C21" s="3">
-        <v>500.0</v>
-      </c>
-      <c r="D21" s="4">
+      <c r="D21" s="3">
+        <v>500.0</v>
+      </c>
+      <c r="E21" s="4">
         <v>0.042847222222222224</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="3">
+        <v>45</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="3">
         <v>20.0</v>
       </c>
-      <c r="C22" s="3">
-        <v>500.0</v>
-      </c>
-      <c r="D22" s="4">
+      <c r="D22" s="3">
+        <v>500.0</v>
+      </c>
+      <c r="E22" s="4">
         <v>0.05572916666666667</v>
       </c>
     </row>
